--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iteration 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iteration 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Iteration 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Iteration 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,10 +686,10 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -723,17 +723,17 @@
           <t>Back Body Blaze
 Vivaran Dhasmana
 38% pred | 0% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Cauveri Vikrant
-38% pred | 0% hist
-[DROP]</t>
+          <t>Back Body Blaze Express
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -817,7 +817,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -871,7 +878,7 @@
       <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Cauveri Vikrant
+Karanvir Bhatia
 38% pred | 0% hist
 [DROP]</t>
         </is>
@@ -908,14 +915,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
@@ -1133,7 +1133,7 @@
           <t>PowerCycle
 Cauveri Vikrant
 45% pred | 0% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1178,9 +1178,9 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Atulan Purohit
-38% pred | 0% hist
+          <t>Barre 57
+Karanvir Bhatia
+27% pred | 27% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1232,11 +1232,11 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+100% pred | 100% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1413,10 +1413,10 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -1450,17 +1450,17 @@
           <t>Back Body Blaze
 Vivaran Dhasmana
 38% pred | 0% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Cauveri Vikrant
-38% pred | 0% hist
-[DROP]</t>
+          <t>Back Body Blaze Express
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -1544,7 +1544,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -1598,7 +1605,7 @@
       <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Cauveri Vikrant
+Karanvir Bhatia
 38% pred | 0% hist
 [DROP]</t>
         </is>
@@ -1635,14 +1642,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
@@ -1860,7 +1860,7 @@
           <t>PowerCycle
 Cauveri Vikrant
 45% pred | 0% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1905,9 +1905,9 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Atulan Purohit
-38% pred | 0% hist
+          <t>Barre 57
+Karanvir Bhatia
+27% pred | 27% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1959,11 +1959,11 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+100% pred | 100% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2140,10 +2140,10 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -2177,17 +2177,17 @@
           <t>Back Body Blaze
 Vivaran Dhasmana
 38% pred | 0% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Cauveri Vikrant
-38% pred | 0% hist
-[DROP]</t>
+          <t>Back Body Blaze Express
+Atulan Purohit
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2271,7 +2271,14 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Reshma Sharma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -2325,7 +2332,7 @@
       <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Cauveri Vikrant
+Karanvir Bhatia
 38% pred | 0% hist
 [DROP]</t>
         </is>
@@ -2362,14 +2369,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
@@ -2587,7 +2587,7 @@
           <t>PowerCycle
 Cauveri Vikrant
 45% pred | 0% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -2632,9 +2632,9 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Atulan Purohit
-38% pred | 0% hist
+          <t>Barre 57
+Karanvir Bhatia
+27% pred | 27% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2686,11 +2686,11 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+100% pred | 100% hist
 [CONSIDER]</t>
         </is>
       </c>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -622,10 +622,10 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Cauveri Vikrant
-38% pred | 0% hist
-[CONSIDER]</t>
+          <t>Cardio Barre
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -648,7 +648,7 @@
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
+Cauveri Vikrant
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -664,34 +664,34 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+46% pred | 46% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
           <t>Mat 57
 Karanvir Bhatia
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-46% pred | 46% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -723,10 +723,17 @@
           <t>Back Body Blaze
 Vivaran Dhasmana
 38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -744,7 +751,14 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -817,14 +831,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -856,7 +863,7 @@
           <t>Recovery
 Vivaran Dhasmana
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -880,15 +887,15 @@
           <t>Recovery
 Karanvir Bhatia
 38% pred | 0% hist
-[DROP]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Cauveri Vikrant
-38% pred | 0% hist
-[DROP]</t>
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -904,7 +911,7 @@
           <t>PowerCycle
 Cauveri Vikrant
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
     </row>
@@ -919,14 +926,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karan Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -979,72 +979,44 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
 15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1053,10 +1025,66 @@
           <t>FIT
 Mrigakshi Jaiswal
 40% pred | 40% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Reshma Sharma
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre Express
 Mrigakshi Jaiswal
@@ -1064,15 +1092,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>FIT
 Atulan Purohit
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>FIT
 Cauveri Vikrant
@@ -1080,7 +1108,7 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
@@ -1088,71 +1116,71 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
 45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
 88% pred | 88% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
 45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
 49% pred | 49% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
 45% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+45% pred | 0% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -1160,23 +1188,23 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
 45% pred | 45% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1184,47 +1212,40 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Richard D'Costa
-35% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karan Bhatia
@@ -1232,15 +1253,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
 Atulan Purohit
-100% pred | 100% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Richard D'Costa
@@ -1248,15 +1269,8 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1272,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1349,10 +1363,10 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Cauveri Vikrant
-38% pred | 0% hist
-[CONSIDER]</t>
+          <t>Cardio Barre
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1375,7 +1389,7 @@
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
+Cauveri Vikrant
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -1391,34 +1405,34 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+46% pred | 46% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
           <t>Mat 57
 Karanvir Bhatia
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-46% pred | 46% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -1450,10 +1464,17 @@
           <t>Back Body Blaze
 Vivaran Dhasmana
 38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -1471,7 +1492,14 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -1544,14 +1572,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -1583,7 +1604,7 @@
           <t>Recovery
 Vivaran Dhasmana
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1607,15 +1628,15 @@
           <t>Recovery
 Karanvir Bhatia
 38% pred | 0% hist
-[DROP]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Cauveri Vikrant
-38% pred | 0% hist
-[DROP]</t>
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1631,7 +1652,7 @@
           <t>PowerCycle
 Cauveri Vikrant
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
     </row>
@@ -1646,14 +1667,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karan Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1706,72 +1720,44 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
 15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1780,10 +1766,66 @@
           <t>FIT
 Mrigakshi Jaiswal
 40% pred | 40% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Reshma Sharma
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre Express
 Mrigakshi Jaiswal
@@ -1791,15 +1833,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>FIT
 Atulan Purohit
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>FIT
 Cauveri Vikrant
@@ -1807,7 +1849,7 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
@@ -1815,71 +1857,71 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
 45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
 88% pred | 88% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
 45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
 49% pred | 49% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
 45% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+45% pred | 0% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -1887,23 +1929,23 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
 45% pred | 45% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1911,47 +1953,40 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Richard D'Costa
-35% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karan Bhatia
@@ -1959,15 +1994,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
 Atulan Purohit
-100% pred | 100% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Richard D'Costa
@@ -1975,15 +2010,8 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1999,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2076,10 +2104,10 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Cauveri Vikrant
-38% pred | 0% hist
-[CONSIDER]</t>
+          <t>Cardio Barre
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -2102,7 +2130,7 @@
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
+Cauveri Vikrant
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -2118,34 +2146,34 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+52% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+46% pred | 46% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
           <t>Mat 57
 Karanvir Bhatia
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-46% pred | 46% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -2177,10 +2205,17 @@
           <t>Back Body Blaze
 Vivaran Dhasmana
 38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -2198,7 +2233,14 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -2271,14 +2313,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -2310,7 +2345,7 @@
           <t>Recovery
 Vivaran Dhasmana
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2334,15 +2369,15 @@
           <t>Recovery
 Karanvir Bhatia
 38% pred | 0% hist
-[DROP]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Cauveri Vikrant
-38% pred | 0% hist
-[DROP]</t>
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -2358,7 +2393,7 @@
           <t>PowerCycle
 Cauveri Vikrant
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
     </row>
@@ -2373,14 +2408,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karan Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2433,72 +2461,44 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Pranjali Jain
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
 15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2507,10 +2507,66 @@
           <t>FIT
 Mrigakshi Jaiswal
 40% pred | 40% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Reshma Sharma
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre Express
 Mrigakshi Jaiswal
@@ -2518,15 +2574,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>FIT
 Atulan Purohit
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>FIT
 Cauveri Vikrant
@@ -2534,7 +2590,7 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karan Bhatia
@@ -2542,71 +2598,71 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
 45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
 88% pred | 88% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
 45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
 49% pred | 49% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
 45% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+45% pred | 0% hist
 [DROP]</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-45% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -2614,23 +2670,23 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
 45% pred | 45% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2638,47 +2694,40 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
 38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Richard D'Costa
-35% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karan Bhatia
@@ -2686,15 +2735,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
 Atulan Purohit
-100% pred | 100% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Richard D'Costa
@@ -2702,15 +2751,8 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -83,12 +83,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,10 +152,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -605,55 +605,83 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-54% pred | 54% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="n"/>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Sovena Shetty
+2% pred | 2% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+29% pred | 29% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+26% pred | 26% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+20% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -661,64 +689,57 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Janhavi Jain
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-36% pred | 36% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Simran Dutt
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Janhavi Jain
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+10% pred | 10% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Sovena Shetty
+60% pred | 60% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Anisha Shah
 85% pred | 85% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-63% pred | 63% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+29% pred | 29% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -726,35 +747,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Richard D'Costa
-81% pred | 81% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -762,24 +755,24 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Janhavi Jain
+Simonelle De Vitre
 9% pred | 9% hist
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-8% pred | 8% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Sovena Shetty
+18% pred | 18% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Simran Dutt
@@ -787,16 +780,23 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
 60% pred | 60% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -804,41 +804,55 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simran Dutt
+8% pred | 8% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+30% pred | 30% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
 27% pred | 27% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-85% pred | 85% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+34% pred | 34% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Vivaran Dhasmana
-0% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+79% pred | 79% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -853,16 +867,23 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Richard D'Costa
-50% pred | 50% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simonelle De Vitre
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Mat 57
@@ -871,16 +892,16 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-64% pred | 64% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Atulan Purohit
+7% pred | 7% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -888,60 +909,88 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Mat 57
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Simran Dutt
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karan Bhatia
-20% pred | 0% hist
-[PINNED]</t>
+47% pred | 47% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-20% pred | 0% hist
-[DROP]</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karan Bhatia
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karan Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Simonelle De Vitre
+4% pred | 4% hist
+[DROP]</t>
         </is>
       </c>
     </row>
@@ -951,9 +1000,23 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karan Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -962,8 +1025,22 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+19% pred | 19% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -979,7 +1056,7 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -987,23 +1064,23 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+32% pred | 32% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Mrigakshi Jaiswal
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-25% pred | 25% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1011,23 +1088,23 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-27% pred | 27% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n"/>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+26% pred | 26% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+14% pred | 14% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -1040,43 +1117,50 @@
           <t>Mat 57
 Karanvir Bhatia
 20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Reshma Sharma
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Simonelle De Vitre
-23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-8% pred | 8% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
+Simran Dutt
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -1089,7 +1173,7 @@
           <t>PowerCycle
 Karan Bhatia
 20% pred | 0% hist
-[CONSIDER]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1103,9 +1187,9 @@
       <c r="D16" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
-Reshma Sharma
-20% pred | 0% hist
-[DROP]</t>
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1119,7 +1203,7 @@
       <c r="F16" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
-Karanvir Bhatia
+Rohan Dahima
 20% pred | 0% hist
 [DROP]</t>
         </is>
@@ -1127,12 +1211,12 @@
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
+Simonelle De Vitre
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -1140,7 +1224,7 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
@@ -1148,7 +1232,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Simonelle De Vitre
@@ -1156,39 +1240,39 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-33% pred | 33% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
 69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+22% pred | 22% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -1196,24 +1280,31 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
 68% pred | 68% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1221,23 +1312,37 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+0% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
 Simonelle De Vitre
-22% pred | 22% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Simran Dutt
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n"/>
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1253,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1328,24 +1433,17 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+29% pred | 29% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1357,12 +1455,12 @@
       <c r="G3" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="n"/>
+Anisha Shah
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1370,10 +1468,10 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -1381,16 +1479,16 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Janhavi Jain
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -1398,26 +1496,26 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-36% pred | 36% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Simran Dutt
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+10% pred | 10% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Sovena Shetty
+60% pred | 60% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>FIT
-Janhavi Jain
+Reshma Sharma
 20% pred | 0% hist
 [DROP]</t>
         </is>
@@ -1427,10 +1525,10 @@
           <t>PowerCycle
 Anisha Shah
 85% pred | 85% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>FIT
 Rohan Dahima
@@ -1438,7 +1536,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1446,7 +1544,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H5" s="6" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1454,8 +1552,8 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>FIT
 Richard D'Costa
@@ -1463,18 +1561,11 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -1482,24 +1573,24 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Janhavi Jain
+Simonelle De Vitre
 9% pred | 9% hist
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-8% pred | 8% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Sovena Shetty
+18% pred | 18% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Simran Dutt
@@ -1507,16 +1598,16 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 60% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Sovena Shetty
+32% pred | 32% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -1524,12 +1615,12 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-27% pred | 27% hist
-[DROP]</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simran Dutt
+8% pred | 8% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1540,25 +1631,39 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+27% pred | 27% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>PowerCycle Express
+          <t>PowerCycle
 Rohan Dahima
-15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Vivaran Dhasmana
-0% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+79% pred | 79% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -1573,8 +1678,15 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simonelle De Vitre
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Richard D'Costa
@@ -1582,7 +1694,14 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1591,16 +1710,16 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-64% pred | 64% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -1608,60 +1727,88 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Simran Dutt
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+56% pred | 56% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karan Bhatia
-20% pred | 0% hist
-[PINNED]</t>
+47% pred | 47% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-20% pred | 0% hist
-[DROP]</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karan Bhatia
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karan Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Richard D'Costa
+3% pred | 3% hist
+[DROP]</t>
         </is>
       </c>
     </row>
@@ -1671,9 +1818,16 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1682,8 +1836,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+19% pred | 19% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1699,7 +1860,7 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1707,71 +1868,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-25% pred | 25% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-27% pred | 27% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
-23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+37% pred | 37% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Simonelle De Vitre
@@ -1779,8 +1884,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1788,31 +1900,108 @@
 [CONSIDER]</t>
         </is>
       </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+14% pred | 14% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+16% pred | 16% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+47% pred | 47% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
 20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -1820,15 +2009,15 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1836,31 +2025,31 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+22% pred | 22% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+Simonelle De Vitre
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
@@ -1868,7 +2057,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Simonelle De Vitre
@@ -1876,23 +2065,23 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-33% pred | 33% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
 69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1900,40 +2089,47 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Sovena Shetty
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
 68% pred | 68% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1941,23 +2137,37 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Simonelle De Vitre
-22% pred | 22% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Simran Dutt
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n"/>
+36% pred | 36% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Simonelle De Vitre
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1973,7 +2183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2045,28 +2255,56 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-41% pred | 41% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Richard D'Costa
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+32% pred | 32% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+29% pred | 29% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2074,26 +2312,26 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -2101,56 +2339,49 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Janhavi Jain
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Sovena Shetty
 30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
-36% pred | 36% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>FIT
-Janhavi Jain
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+Reshma Sharma
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Anisha Shah
 85% pred | 85% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>FIT
 Rohan Dahima
@@ -2158,7 +2389,7 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -2166,60 +2397,60 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Sovena Shetty
+7% pred | 7% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Simonelle De Vitre
+9% pred | 9% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>FIT
-Richard D'Costa
-81% pred | 81% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Simran Dutt
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Janhavi Jain
-9% pred | 9% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+Pranjali Jain
+77% pred | 77% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karan Bhatia
-8% pred | 8% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+21% pred | 21% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Simran Dutt
@@ -2227,58 +2458,65 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 60% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Simonelle De Vitre
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simran Dutt
+8% pred | 8% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Sovena Shetty
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
 27% pred | 27% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-85% pred | 85% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Rohan Dahima
-15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
-Vivaran Dhasmana
-0% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+79% pred | 79% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -2287,23 +2525,37 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
 Richard D'Costa
-50% pred | 50% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="9" t="inlineStr">
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2311,56 +2563,56 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-64% pred | 64% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Sovena Shetty
+77% pred | 77% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+25% pred | 25% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Karan Bhatia
-20% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-20% pred | 0% hist
-[DROP]</t>
+47% pred | 47% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -2370,18 +2622,25 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Recovery
+Rohan Dahima
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
 Karan Bhatia
 20% pred | 0% hist
-[CONSIDER]</t>
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -2391,9 +2650,16 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
       <c r="E13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2402,8 +2668,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Simonelle De Vitre
+19% pred | 19% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -2414,12 +2687,33 @@
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2427,80 +2721,87 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
 36% pred | 36% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-25% pred | 25% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+41% pred | 41% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Atulan Purohit
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-27% pred | 27% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+17% pred | 17% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+16% pred | 16% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Simonelle De Vitre
+14% pred | 14% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
 20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="9" t="inlineStr">
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Mrigakshi Jaiswal
+28% pred | 28% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Reshma Sharma
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -2508,31 +2809,52 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Mat 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+Simran Dutt
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+47% pred | 47% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
 20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -2540,15 +2862,15 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -2556,31 +2878,31 @@
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+Simonelle De Vitre
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
@@ -2588,7 +2910,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Simonelle De Vitre
@@ -2596,64 +2918,64 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-33% pred | 33% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+19% pred | 19% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
 69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simran Dutt
+22% pred | 22% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
 68% pred | 68% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Reshma Sharma
-20% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="inlineStr">
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Simonelle De Vitre
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -2661,23 +2983,37 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Simonelle De Vitre
-22% pred | 22% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Simran Dutt
-20% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n"/>
+36% pred | 36% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Mrigakshi Jaiswal
+56% pred | 56% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Richard D'Costa
+Rohan Dahima
 42% pred | 0% hist
 []</t>
         </is>
@@ -681,19 +681,12 @@
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-44% pred | 0% hist
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+30% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -703,10 +696,66 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Reshma Sharma
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -714,8 +763,8 @@
 []</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -723,76 +772,6 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-59% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
@@ -801,60 +780,60 @@
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+88% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
@@ -862,45 +841,108 @@
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Vivaran Dhasmana
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -908,7 +950,7 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -917,15 +959,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -933,7 +975,7 @@
 []</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -941,17 +983,17 @@
 []</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -959,7 +1001,7 @@
 []</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -967,7 +1009,7 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -975,7 +1017,7 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -983,8 +1025,8 @@
 []</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -992,54 +1034,12 @@
 []</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -1047,41 +1047,48 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
 55% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1089,7 +1096,49 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1097,16 +1146,16 @@
 []</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1114,26 +1163,33 @@
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1141,48 +1197,41 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1190,100 +1239,30 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>19:15</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
@@ -1291,10 +1270,87 @@
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
@@ -1302,8 +1358,8 @@
 []</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1311,7 +1367,7 @@
 []</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -1319,25 +1375,18 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -1345,11 +1394,11 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1365,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1453,7 +1502,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Richard D'Costa
+Rohan Dahima
 42% pred | 0% hist
 []</t>
         </is>
@@ -1513,19 +1562,12 @@
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-44% pred | 0% hist
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+30% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1535,10 +1577,66 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Reshma Sharma
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1546,8 +1644,8 @@
 []</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1555,76 +1653,6 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-59% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
@@ -1633,60 +1661,60 @@
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+88% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
@@ -1694,45 +1722,108 @@
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Vivaran Dhasmana
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -1740,7 +1831,7 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -1749,15 +1840,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1765,7 +1856,7 @@
 []</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -1773,17 +1864,17 @@
 []</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1791,7 +1882,7 @@
 []</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1799,7 +1890,7 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1807,7 +1898,7 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -1815,8 +1906,8 @@
 []</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1824,54 +1915,12 @@
 []</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -1879,41 +1928,48 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
 55% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1921,7 +1977,49 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1929,16 +2027,16 @@
 []</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -1946,26 +2044,33 @@
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1973,48 +2078,41 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2022,100 +2120,30 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>19:15</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
@@ -2123,10 +2151,87 @@
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
@@ -2134,8 +2239,8 @@
 []</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2143,7 +2248,7 @@
 []</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2151,25 +2256,18 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -2177,11 +2275,11 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2197,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2285,7 +2383,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Richard D'Costa
+Rohan Dahima
 42% pred | 0% hist
 []</t>
         </is>
@@ -2345,19 +2443,12 @@
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-44% pred | 0% hist
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+30% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2367,10 +2458,66 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Reshma Sharma
+13% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2378,8 +2525,8 @@
 []</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -2387,76 +2534,6 @@
 []</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-59% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-69% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
@@ -2465,60 +2542,60 @@
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+59% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+37% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+77% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+88% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
@@ -2526,45 +2603,108 @@
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Anisha Shah
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Vivaran Dhasmana
+17% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -2572,7 +2712,7 @@
 []</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karan Bhatia
@@ -2581,15 +2721,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -2597,7 +2737,7 @@
 []</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -2605,17 +2745,17 @@
 []</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -2623,7 +2763,7 @@
 []</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -2631,7 +2771,7 @@
 []</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2639,7 +2779,7 @@
 []</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -2647,8 +2787,8 @@
 []</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -2656,54 +2796,12 @@
 []</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -2711,41 +2809,48 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
 55% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -2753,7 +2858,49 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2761,16 +2908,16 @@
 []</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Karanvir Bhatia
@@ -2778,26 +2925,33 @@
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2805,48 +2959,41 @@
 []</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+27% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2854,100 +3001,30 @@
 []</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Pranjali Jain
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>19:15</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+29% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
@@ -2955,10 +3032,87 @@
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+23% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+15% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
@@ -2966,8 +3120,8 @@
 []</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2975,7 +3129,7 @@
 []</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2983,25 +3137,18 @@
 []</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -3009,11 +3156,11 @@
 []</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -613,8 +613,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
@@ -622,8 +622,8 @@
         <is>
           <t>FIT
 Rohan Dahima
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -640,8 +640,8 @@
         <is>
           <t>Mat 57
 Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -649,8 +649,8 @@
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -668,16 +668,16 @@
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
@@ -686,11 +686,18 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n"/>
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+7% pred | 7% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -706,9 +713,9 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
+Karanvir Bhatia
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -726,8 +733,8 @@
         <is>
           <t>PowerCycle Express
 Reshma Sharma
-13% pred | 0% hist
-[]</t>
+13% pred | 13% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -735,7 +742,7 @@
           <t>PowerCycle
 Rohan Dahima
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -744,7 +751,7 @@
           <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -759,8 +766,8 @@
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-43% pred | 0% hist
-[]</t>
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -768,8 +775,8 @@
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -787,8 +794,8 @@
         <is>
           <t>Cardio Barre
 Reshma Sharma
-59% pred | 0% hist
-[]</t>
+59% pred | 59% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
@@ -796,24 +803,24 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
-37% pred | 0% hist
-[]</t>
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 0% hist
-[]</t>
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -830,8 +837,8 @@
         <is>
           <t>FIT
 Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
+88% pred | 88% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
@@ -851,8 +858,8 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
@@ -860,16 +867,16 @@
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Vivaran Dhasmana
-17% pred | 0% hist
-[]</t>
+17% pred | 17% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -885,8 +892,8 @@
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -906,8 +913,8 @@
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -918,16 +925,16 @@
         <is>
           <t>Barre 57
 Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -946,16 +953,16 @@
         <is>
           <t>FIT
 Atulan Purohit
-82% pred | 0% hist
-[]</t>
+82% pred | 82% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
-47% pred | 0% hist
-[]</t>
+Pranjali Jain
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -971,16 +978,16 @@
         <is>
           <t>PowerCycle
 Reshma Sharma
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -997,41 +1004,48 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-51% pred | 0% hist
-[]</t>
+51% pred | 51% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H16" s="5" t="n"/>
@@ -1042,25 +1056,39 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
+          <t>Barre 57
+Pranjali Jain
+43% pred | 43% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
@@ -1077,8 +1105,8 @@
         <is>
           <t>PowerCycle Express
 Anisha Shah
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -1100,8 +1128,8 @@
         <is>
           <t>Recovery
 Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H19" s="5" t="n"/>
@@ -1122,8 +1150,8 @@
         <is>
           <t>PowerCycle Express
 Richard D'Costa
-14% pred | 0% hist
-[]</t>
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -1142,8 +1170,8 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H21" s="5" t="n"/>
@@ -1155,20 +1183,20 @@
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -1176,8 +1204,8 @@
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G22" s="5" t="n"/>
@@ -1193,16 +1221,16 @@
         <is>
           <t>PowerCycle
 Anmol Sharma
-24% pred | 0% hist
-[]</t>
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
+20% pred | 20% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
@@ -1210,19 +1238,26 @@
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n"/>
+27% pred | 27% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
@@ -1235,8 +1270,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -1258,13 +1293,20 @@
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Rohan Dahima
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
@@ -1278,25 +1320,32 @@
         <is>
           <t>Barre 57
 Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n"/>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Rohan Dahima
-23% pred | 0% hist
-[]</t>
+Cauveri Vikrant
+23% pred | 23% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G26" s="5" t="n"/>
@@ -1309,36 +1358,36 @@
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Cauveri Vikrant
-15% pred | 0% hist
-[]</t>
+Rohan Dahima
+15% pred | 15% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G27" s="5" t="n"/>
@@ -1354,8 +1403,8 @@
         <is>
           <t>PowerCycle
 Karan Bhatia
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -1363,20 +1412,27 @@
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-21% pred | 0% hist
-[]</t>
+21% pred | 21% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
-71% pred | 0% hist
-[]</t>
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H28" s="5" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
@@ -1390,8 +1446,8 @@
         <is>
           <t>Recovery
 Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
@@ -1414,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1494,8 +1550,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
@@ -1503,8 +1559,8 @@
         <is>
           <t>FIT
 Rohan Dahima
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -1521,8 +1577,8 @@
         <is>
           <t>Mat 57
 Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -1530,8 +1586,8 @@
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -1549,16 +1605,16 @@
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
@@ -1567,8 +1623,8 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -1587,389 +1643,396 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
+Karanvir Bhatia
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Reshma Sharma
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-43% pred | 0% hist
-[]</t>
+59% pred | 59% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+          <t>Barre 57
+Reshma Sharma
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-59% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
-Atulan Purohit
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Mrigakshi Jaiswal
+88% pred | 88% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Vivaran Dhasmana
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+17% pred | 17% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-49% pred | 0% hist
-[]</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
+          <t>FIT
+Atulan Purohit
+82% pred | 82% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-82% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+51% pred | 51% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Pranjali Jain
+33% pred | 33% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-51% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
+          <t>Cardio Barre
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
+43% pred | 43% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1977,20 +2040,20 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -1998,33 +2061,61 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+17% pred | 17% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-34% pred | 0% hist
-[]</t>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 20% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H21" s="5" t="n"/>
@@ -2032,33 +2123,40 @@
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
+20% pred | 20% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+27% pred | 27% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G22" s="5" t="n"/>
@@ -2067,117 +2165,131 @@
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
       <c r="D23" s="5" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-27% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Rohan Dahima
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+23% pred | 23% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
+Richard D'Costa
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-23% pred | 0% hist
-[]</t>
+15% pred | 15% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="G26" s="5" t="n"/>
@@ -2186,100 +2298,58 @@
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+21% pred | 21% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-21% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
 Karanvir Bhatia
-71% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2375,8 +2445,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
@@ -2384,8 +2454,8 @@
         <is>
           <t>FIT
 Rohan Dahima
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -2402,8 +2472,8 @@
         <is>
           <t>Mat 57
 Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -2411,8 +2481,8 @@
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -2430,16 +2500,16 @@
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
@@ -2448,8 +2518,8 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -2469,8 +2539,8 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -2488,25 +2558,18 @@
         <is>
           <t>PowerCycle Express
 Reshma Sharma
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+13% pred | 13% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -2521,8 +2584,8 @@
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-43% pred | 0% hist
-[]</t>
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -2530,8 +2593,8 @@
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -2549,8 +2612,8 @@
         <is>
           <t>Cardio Barre
 Reshma Sharma
-59% pred | 0% hist
-[]</t>
+59% pred | 59% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
@@ -2558,24 +2621,24 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
-37% pred | 0% hist
-[]</t>
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 0% hist
-[]</t>
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -2592,8 +2655,8 @@
         <is>
           <t>FIT
 Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
+88% pred | 88% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
@@ -2613,8 +2676,8 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
@@ -2622,16 +2685,16 @@
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Vivaran Dhasmana
-17% pred | 0% hist
-[]</t>
+17% pred | 17% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -2647,8 +2710,8 @@
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -2668,8 +2731,8 @@
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -2680,16 +2743,16 @@
         <is>
           <t>Barre 57
 Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -2708,16 +2771,16 @@
         <is>
           <t>FIT
 Atulan Purohit
-82% pred | 0% hist
-[]</t>
+82% pred | 82% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
-47% pred | 0% hist
-[]</t>
+Pranjali Jain
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -2733,16 +2796,16 @@
         <is>
           <t>PowerCycle
 Reshma Sharma
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -2759,44 +2822,58 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-51% pred | 0% hist
-[]</t>
+51% pred | 51% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -2813,16 +2890,16 @@
         <is>
           <t>Barre 57
 Atulan Purohit
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Atulan Purohit
-28% pred | 0% hist
-[]</t>
+          <t>Barre 57
+Rohan Dahima
+43% pred | 43% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
@@ -2839,8 +2916,8 @@
         <is>
           <t>PowerCycle Express
 Anisha Shah
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -2862,8 +2939,8 @@
         <is>
           <t>Recovery
 Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H19" s="5" t="n"/>
@@ -2884,8 +2961,8 @@
         <is>
           <t>PowerCycle Express
 Richard D'Costa
-14% pred | 0% hist
-[]</t>
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -2904,8 +2981,8 @@
         <is>
           <t>PowerCycle
 Rohan Dahima
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H21" s="5" t="n"/>
@@ -2916,21 +2993,28 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[]</t>
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -2938,11 +3022,18 @@
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n"/>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
@@ -2955,33 +3046,40 @@
         <is>
           <t>PowerCycle
 Anmol Sharma
-24% pred | 0% hist
-[]</t>
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
+20% pred | 20% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
-27% pred | 0% hist
-[]</t>
+27% pred | 27% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G23" s="5" t="n"/>
@@ -2997,8 +3095,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -3020,13 +3118,20 @@
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Rohan Dahima
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
@@ -3040,25 +3145,32 @@
         <is>
           <t>Barre 57
 Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n"/>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
-23% pred | 0% hist
-[]</t>
+23% pred | 23% hist
+[DROP]</t>
         </is>
       </c>
       <c r="G26" s="5" t="n"/>
@@ -3071,36 +3183,36 @@
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Cauveri Vikrant
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-15% pred | 0% hist
-[]</t>
+15% pred | 15% hist
+[DROP]</t>
         </is>
       </c>
       <c r="G27" s="5" t="n"/>
@@ -3112,12 +3224,12 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-47% pred | 0% hist
-[]</t>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+28% pred | 28% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -3125,16 +3237,16 @@
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-21% pred | 0% hist
-[]</t>
+21% pred | 21% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
-71% pred | 0% hist
-[]</t>
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -3152,8 +3264,8 @@
         <is>
           <t>Recovery
 Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -549,7 +549,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Max Score  |  Week of 2026-05-11</t>
+          <t>Supreme HQ, Bandra  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -562,43 +562,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <is>
           <t>FIT
 Rohan Dahima
-42% pred | 42% hist
+41% pred | 41% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -676,7 +676,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 58% hist
+59% pred | 59% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -690,14 +690,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-7% pred | 7% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -713,8 +706,8 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Karanvir Bhatia
-17% pred | 17% hist
+Vivaran Dhasmana
+47% pred | 47% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -729,27 +722,13 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-13% pred | 13% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -819,7 +798,7 @@
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 77% hist
+76% pred | 76% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -854,12 +833,12 @@
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-49% pred | 49% hist
-[CONSIDER]</t>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
@@ -879,7 +858,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
@@ -929,12 +915,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 68% hist
-[PROTECT_EXACT]</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -1018,10 +1004,10 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
+          <t>Cardio Barre Plus
+Pranjali Jain
+33% pred | 33% hist
+[DROP]</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1036,7 +1022,7 @@
         <is>
           <t>Mat 57
 Pranjali Jain
-45% pred | 45% hist
+43% pred | 43% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1048,7 +1034,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -1056,14 +1049,7 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
@@ -1083,12 +1069,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-43% pred | 43% hist
-[CONSIDER]</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1172,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Reshma Sharma
+Rohan Dahima
 29% pred | 29% hist
 [CONSIDER]</t>
         </is>
@@ -1195,7 +1181,7 @@
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-17% pred | 17% hist
+15% pred | 15% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1233,12 +1219,19 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 30% hist
+29% pred | 29% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1399,12 +1392,12 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+28% pred | 28% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -1425,14 +1418,7 @@
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
@@ -1470,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1486,7 +1472,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Trainer Hours  |  Week of 2026-05-11</t>
+          <t>Supreme HQ, Bandra  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1499,43 +1485,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1545,7 @@
         <is>
           <t>FIT
 Rohan Dahima
-42% pred | 42% hist
+41% pred | 41% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1613,7 +1599,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 58% hist
+59% pred | 59% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1652,12 +1638,47 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Reshma Sharma
+13% pred | 13% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1665,8 +1686,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1674,18 +1695,18 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -1693,8 +1714,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1702,7 +1723,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1710,25 +1731,25 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 77% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+76% pred | 76% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -1736,20 +1757,20 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -1757,8 +1778,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1766,7 +1787,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Vivaran Dhasmana
@@ -1774,7 +1795,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1782,40 +1803,19 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
 49% pred | 49% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 33% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1823,43 +1823,64 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-68% pred | 68% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
           <t>FIT
 Atulan Purohit
 82% pred | 82% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pranjali Jain
@@ -1868,15 +1889,15 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1884,7 +1905,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -1892,17 +1913,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1910,7 +1931,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1918,15 +1939,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Pranjali Jain
-33% pred | 33% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -1934,15 +1955,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1950,27 +1971,34 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Mrigakshi Jaiswal
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1978,25 +2006,25 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-43% pred | 43% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Anisha Shah
@@ -2004,35 +2032,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 55% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -2040,20 +2047,20 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -2061,7 +2068,28 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2069,23 +2097,16 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Rohan Dahima
@@ -2093,16 +2114,16 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-17% pred | 17% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2110,7 +2131,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -2118,15 +2139,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2134,7 +2155,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2142,16 +2163,16 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2159,16 +2180,16 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2176,22 +2197,22 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -2199,9 +2220,9 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -2209,16 +2230,23 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2226,7 +2254,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -2234,7 +2262,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
@@ -2242,25 +2270,32 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
 23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
@@ -2268,7 +2303,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2276,7 +2311,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2284,24 +2319,24 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Rohan Dahima
+Cauveri Vikrant
 15% pred | 15% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
@@ -2309,8 +2344,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2318,7 +2353,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2326,18 +2361,18 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -2345,11 +2380,11 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2381,7 +2416,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Class Variety  |  Week of 2026-05-11</t>
+          <t>Supreme HQ, Bandra  |  Class Variety  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2394,43 +2429,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2489,7 @@
         <is>
           <t>FIT
 Rohan Dahima
-42% pred | 42% hist
+41% pred | 41% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2508,7 +2543,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 58% hist
+59% pred | 59% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2538,8 +2573,8 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Vivaran Dhasmana
-47% pred | 47% hist
+Karanvir Bhatia
+17% pred | 17% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2637,7 +2672,7 @@
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 77% hist
+76% pred | 76% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2778,7 +2813,7 @@
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
+Reshma Sharma
 49% pred | 49% hist
 [PROTECT_EXACT]</t>
         </is>
@@ -2854,7 +2889,7 @@
         <is>
           <t>Mat 57
 Pranjali Jain
-45% pred | 45% hist
+43% pred | 43% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2866,14 +2901,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -2896,10 +2924,10 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-43% pred | 43% hist
-[CONSIDER]</t>
+          <t>Cardio Barre
+Reshma Sharma
+28% pred | 28% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3032,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Reshma Sharma
+Atulan Purohit
 29% pred | 29% hist
 [CONSIDER]</t>
         </is>
@@ -3013,7 +3041,7 @@
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-17% pred | 17% hist
+15% pred | 15% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -3058,19 +3086,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Rohan Dahima
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="D23" s="5" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 30% hist
+29% pred | 29% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -3173,7 +3194,14 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
@@ -3224,12 +3252,12 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-28% pred | 28% hist
-[CONSIDER]</t>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -549,7 +549,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Supreme HQ, Bandra  |  Max Score  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -562,43 +562,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <is>
           <t>FIT
 Rohan Dahima
-41% pred | 41% hist
+42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -676,7 +676,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-59% pred | 59% hist
+58% pred | 58% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -722,17 +722,17 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Reshma Sharma
+13% pred | 13% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -798,7 +798,7 @@
         <is>
           <t>FIT
 Atulan Purohit
-76% pred | 76% hist
+77% pred | 77% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -915,12 +915,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -1004,10 +1004,10 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Pranjali Jain
-33% pred | 33% hist
-[DROP]</t>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1022,7 +1022,7 @@
         <is>
           <t>Mat 57
 Pranjali Jain
-43% pred | 43% hist
+45% pred | 45% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1034,14 +1034,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -1053,14 +1046,7 @@
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1181,7 +1167,7 @@
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-15% pred | 15% hist
+17% pred | 17% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1194,7 +1180,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
@@ -1219,36 +1212,29 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+27% pred | 27% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Rohan Dahima
+Pranjali Jain
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-27% pred | 27% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-24% pred | 24% hist
-[CONSIDER]</t>
         </is>
       </c>
       <c r="H23" s="5" t="n"/>
@@ -1472,7 +1458,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Supreme HQ, Bandra  |  Trainer Hours  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1485,43 +1471,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1531,7 @@
         <is>
           <t>FIT
 Rohan Dahima
-41% pred | 41% hist
+42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1599,7 +1585,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-59% pred | 59% hist
+58% pred | 58% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1613,7 +1599,14 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+7% pred | 7% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -1662,10 +1655,10 @@
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -1735,7 +1728,7 @@
         <is>
           <t>FIT
 Atulan Purohit
-76% pred | 76% hist
+77% pred | 77% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1770,12 +1763,12 @@
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+49% pred | 49% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
@@ -1795,14 +1788,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 60% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
@@ -1959,7 +1945,7 @@
         <is>
           <t>Mat 57
 Pranjali Jain
-43% pred | 43% hist
+45% pred | 45% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1971,14 +1957,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -1986,18 +1965,18 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2006,12 +1985,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+43% pred | 43% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
@@ -2105,11 +2084,18 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Rohan Dahima
+Reshma Sharma
 29% pred | 29% hist
 [CONSIDER]</t>
         </is>
@@ -2131,14 +2117,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
@@ -2168,7 +2147,7 @@
         <is>
           <t>Barre 57
 Atulan Purohit
-29% pred | 29% hist
+30% pred | 30% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2180,7 +2159,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
@@ -2238,14 +2224,7 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2273,19 +2252,12 @@
       <c r="F26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Rohan Dahima
+Cauveri Vikrant
 23% pred | 23% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
@@ -2322,9 +2294,9 @@
       <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Cauveri Vikrant
+Rohan Dahima
 15% pred | 15% hist
-[CONSIDER]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="G27" s="5" t="n"/>
@@ -2416,7 +2388,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Supreme HQ, Bandra  |  Class Variety  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2429,43 +2401,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2461,7 @@
         <is>
           <t>FIT
 Rohan Dahima
-41% pred | 41% hist
+42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2543,7 +2515,7 @@
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-59% pred | 59% hist
+58% pred | 58% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2557,7 +2529,14 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -2573,8 +2552,8 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Karanvir Bhatia
-17% pred | 17% hist
+Vivaran Dhasmana
+47% pred | 47% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2589,24 +2568,17 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-13% pred | 13% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -2672,7 +2644,7 @@
         <is>
           <t>FIT
 Atulan Purohit
-76% pred | 76% hist
+77% pred | 77% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2813,8 +2785,8 @@
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Reshma Sharma
-49% pred | 49% hist
+Karan Bhatia
+47% pred | 47% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2871,10 +2843,10 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
+          <t>Cardio Barre Plus
+Pranjali Jain
+33% pred | 33% hist
+[DROP]</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -2889,7 +2861,7 @@
         <is>
           <t>Mat 57
 Pranjali Jain
-43% pred | 43% hist
+45% pred | 45% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2901,7 +2873,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -2924,10 +2903,10 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Reshma Sharma
-28% pred | 28% hist
-[INCLUDE]</t>
+          <t>Barre 57
+Atulan Purohit
+43% pred | 43% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3011,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Atulan Purohit
+Reshma Sharma
 29% pred | 29% hist
 [CONSIDER]</t>
         </is>
@@ -3041,7 +3020,7 @@
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-15% pred | 15% hist
+17% pred | 17% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -3091,7 +3070,7 @@
         <is>
           <t>Barre 57
 Atulan Purohit
-29% pred | 29% hist
+30% pred | 30% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -3194,14 +3173,7 @@
 [DROP]</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
@@ -3252,12 +3224,12 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+28% pred | 28% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Rohan Dahima
+Richard D'Costa
 42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
@@ -715,19 +715,26 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-13% pred | 13% hist
-[CONSIDER]</t>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -736,40 +743,12 @@
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-43% pred | 43% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -777,8 +756,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -786,7 +765,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -794,7 +773,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -802,17 +781,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -820,20 +799,20 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -841,8 +820,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -850,15 +829,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Vivaran Dhasmana
-17% pred | 17% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+Karan Bhatia
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -866,19 +845,40 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
 49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -886,81 +886,60 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 68% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
           <t>FIT
 Atulan Purohit
 82% pred | 82% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -968,7 +947,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -976,17 +955,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -994,7 +973,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1002,7 +981,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1010,7 +989,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -1018,7 +997,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1026,7 +1005,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1034,61 +1013,82 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-55% pred | 55% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-56% pred | 56% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1096,20 +1096,20 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 55% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -1117,28 +1117,7 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -1146,24 +1125,24 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Rohan Dahima
-29% pred | 29% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+53% pred | 53% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
@@ -1171,8 +1150,8 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1180,11 +1159,53 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+20% pred | 20% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
+          <t>Cardio Barre
 Reshma Sharma
-20% pred | 20% hist
+24% pred | 24% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1193,59 +1214,10 @@
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-24% pred | 24% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-20% pred | 20% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-27% pred | 27% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1253,32 +1225,32 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -1286,16 +1258,16 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1303,7 +1275,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
@@ -1311,7 +1283,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Pranjali Jain
@@ -1319,12 +1291,47 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-23% pred | 23% hist
-[CONSIDER]</t>
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Richard D'Costa
+24% pred | 24% hist
+[DROP]</t>
         </is>
       </c>
       <c r="G26" s="5" t="n"/>
@@ -1333,61 +1340,19 @@
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Rohan Dahima
-15% pred | 15% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-28% pred | 28% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1395,7 +1360,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -1403,30 +1368,30 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1442,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1530,7 +1495,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Rohan Dahima
+Richard D'Costa
 42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
@@ -1599,14 +1564,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-7% pred | 7% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -1622,8 +1580,8 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Karanvir Bhatia
-17% pred | 17% hist
+Vivaran Dhasmana
+47% pred | 47% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1631,47 +1589,12 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-13% pred | 13% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1679,8 +1602,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1688,18 +1611,18 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -1707,8 +1630,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1716,7 +1639,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1724,7 +1647,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>FIT
 Atulan Purohit
@@ -1732,17 +1655,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
@@ -1750,29 +1673,29 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-49% pred | 49% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1780,28 +1703,56 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
+Karan Bhatia
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
-17% pred | 17% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
 49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1809,81 +1760,60 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 68% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
           <t>FIT
 Atulan Purohit
 82% pred | 82% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1891,7 +1821,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -1899,17 +1829,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
@@ -1917,7 +1847,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -1925,7 +1855,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1933,7 +1863,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
@@ -1941,7 +1871,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
@@ -1949,7 +1879,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
@@ -1957,68 +1887,103 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-55% pred | 55% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-43% pred | 43% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -2026,20 +1991,20 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 55% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -2047,28 +2012,7 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Rohan Dahima
@@ -2076,15 +2020,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Atulan Purohit
@@ -2092,24 +2036,24 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Reshma Sharma
+Rohan Dahima
 29% pred | 29% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+17% pred | 17% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2117,33 +2061,33 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-24% pred | 24% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
 20% pred | 20% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -2151,15 +2095,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-27% pred | 27% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -2167,15 +2111,15 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2183,32 +2127,32 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
@@ -2216,44 +2160,86 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pranjali Jain
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+23% pred | 23% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-47% pred | 47% hist
+Richard D'Costa
+35% pred | 35% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-23% pred | 23% hist
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Richard D'Costa
+24% pred | 24% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2263,61 +2249,19 @@
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="6" t="inlineStr">
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Rohan Dahima
-15% pred | 15% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
+28% pred | 28% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2325,7 +2269,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2333,30 +2277,30 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2460,7 +2404,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>FIT
-Rohan Dahima
+Richard D'Costa
 42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
@@ -2529,14 +2473,7 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
@@ -2552,8 +2489,8 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Vivaran Dhasmana
-47% pred | 47% hist
+Karanvir Bhatia
+17% pred | 17% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2568,15 +2505,15 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Karan Bhatia
+13% pred | 13% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
@@ -2699,8 +2636,8 @@
       <c r="F11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Vivaran Dhasmana
-17% pred | 17% hist
+Karan Bhatia
+15% pred | 15% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2754,12 +2691,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -2843,10 +2780,10 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Pranjali Jain
-33% pred | 33% hist
-[DROP]</t>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -2873,14 +2810,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -2903,10 +2833,10 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Atulan Purohit
-43% pred | 43% hist
-[CONSIDER]</t>
+          <t>Cardio Barre
+Vivaran Dhasmana
+28% pred | 28% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -3000,14 +2930,7 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -3033,14 +2956,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
@@ -3052,8 +2968,8 @@
       <c r="B23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
-24% pred | 24% hist
+Karan Bhatia
+34% pred | 34% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -3077,12 +2993,19 @@
       <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
-27% pred | 27% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n"/>
+Richard D'Costa
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
@@ -3207,14 +3130,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-15% pred | 15% hist
-[DROP]</t>
-        </is>
-      </c>
+      <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
@@ -3224,12 +3140,12 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-28% pred | 28% hist
-[CONSIDER]</t>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -47,6 +47,10 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
@@ -54,10 +58,6 @@
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -93,17 +93,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,10 +160,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -549,7 +549,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Supreme HQ, Bandra  |  Max Score  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -562,43 +562,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -615,8 +615,8 @@
         <is>
           <t>FIT
 Richard D'Costa
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -629,14 +629,21 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -650,29 +657,29 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-69% pred | 0% hist
-[]</t>
+69% pred | 69% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -689,19 +696,19 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+31% pred | 31% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
@@ -711,16 +718,16 @@
         <is>
           <t>Barre 57
 Rohan Dahima
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-13% pred | 0% hist
-[]</t>
+Reshma Sharma
+13% pred | 13% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -734,12 +741,12 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
-22% pred | 0% hist
-[]</t>
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -747,8 +754,8 @@
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -757,7 +764,7 @@
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -766,8 +773,8 @@
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-86% pred | 0% hist
-[]</t>
+86% pred | 86% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
@@ -775,25 +782,32 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
-93% pred | 0% hist
-[]</t>
+93% pred | 93% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H9" s="5" t="n"/>
@@ -805,21 +819,21 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anisha Shah
-85% pred | 0% hist
-[]</t>
+85% pred | 85% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F10" s="5" t="n"/>
@@ -827,7 +841,7 @@
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -837,33 +851,33 @@
         <is>
           <t>FIT
 Vivaran Dhasmana
-92% pred | 0% hist
-[]</t>
+92% pred | 92% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Mrigakshi Jaiswal
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+77% pred | 77% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
+Rohan Dahima
+17% pred | 17% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H11" s="5" t="n"/>
@@ -878,8 +892,8 @@
         <is>
           <t>Cardio Barre
 Atulan Purohit
-64% pred | 0% hist
-[]</t>
+64% pred | 64% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -895,12 +909,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -911,21 +925,21 @@
         <is>
           <t>Barre 57
 Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
+68% pred | 68% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
@@ -939,16 +953,16 @@
         <is>
           <t>FIT
 Rohan Dahima
-90% pred | 0% hist
-[]</t>
+90% pred | 90% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
+100% pred | 100% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
@@ -963,24 +977,24 @@
         <is>
           <t>Cardio Barre
 Reshma Sharma
-21% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
+21% pred | 21% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -988,7 +1002,7 @@
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
@@ -997,54 +1011,54 @@
         <is>
           <t>Barre 57
 Simran Dutt
-64% pred | 0% hist
-[]</t>
+64% pred | 64% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -1054,13 +1068,20 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-56% pred | 0% hist
-[]</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+73% pred | 73% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+28% pred | 28% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1094,12 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Anisha Shah
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -1100,8 +1121,8 @@
         <is>
           <t>Recovery
 Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H19" s="5" t="n"/>
@@ -1118,12 +1139,12 @@
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Richard D'Costa
-14% pred | 0% hist
-[]</t>
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1159,12 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-19% pred | 0% hist
-[]</t>
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H21" s="5" t="n"/>
@@ -1155,12 +1176,12 @@
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
@@ -1170,7 +1191,7 @@
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
@@ -1179,82 +1200,89 @@
         <is>
           <t>Barre 57
 Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n"/>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E23" s="5" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Reshma Sharma
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-34% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
 Richard D'Costa
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n"/>
+29% pred | 29% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -1263,8 +1291,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -1285,8 +1313,8 @@
         <is>
           <t>Barre 57
 Karanvir Bhatia
-46% pred | 0% hist
-[]</t>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
@@ -1296,7 +1324,7 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
@@ -1306,59 +1334,66 @@
         <is>
           <t>Barre 57
 Karan Bhatia
-100% pred | 0% hist
-[]</t>
+100% pred | 100% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-23% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+23% pred | 23% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+53% pred | 53% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -1366,34 +1401,34 @@
       <c r="H28" s="5" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-21% pred | 0% hist
-[]</t>
+21% pred | 21% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pranjali Jain
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F29" s="5" t="n"/>
@@ -1411,8 +1446,8 @@
         <is>
           <t>Recovery
 Mrigakshi Jaiswal
-56% pred | 0% hist
-[]</t>
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
@@ -1435,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1451,7 +1486,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Supreme HQ, Bandra  |  Trainer Hours  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1464,43 +1499,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -1517,8 +1552,8 @@
         <is>
           <t>FIT
 Richard D'Costa
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -1531,14 +1566,21 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -1552,29 +1594,29 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-69% pred | 0% hist
-[]</t>
+69% pred | 69% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -1591,38 +1633,38 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Rohan Dahima
+31% pred | 31% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Karan Bhatia
-13% pred | 0% hist
-[]</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -1631,366 +1673,359 @@
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-22% pred | 0% hist
-[]</t>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Cauveri Vikrant
+86% pred | 86% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
+          <t>Barre 57
+Reshma Sharma
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+93% pred | 93% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 49% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Cauveri Vikrant
-86% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-93% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
+92% pred | 92% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>PowerCycle
-Anisha Shah
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-92% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
           <t>Mat 57
 Mrigakshi Jaiswal
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+77% pred | 77% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
+Rohan Dahima
+17% pred | 17% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+64% pred | 64% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-64% pred | 0% hist
-[]</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
+          <t>FIT
+Rohan Dahima
+90% pred | 90% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
           <t>Barre 57
 Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
+100% pred | 100% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
-90% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Reshma Sharma
-21% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
-64% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+64% pred | 64% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+73% pred | 73% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1998,20 +2033,20 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -2019,157 +2054,164 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-19% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="6" t="inlineStr">
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
+17% pred | 17% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+16% pred | 16% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-34% pred | 0% hist
-[]</t>
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
@@ -2177,90 +2219,111 @@
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
+Karan Bhatia
+100% pred | 100% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
 Karanvir Bhatia
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+58% pred | 58% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-100% pred | 0% hist
-[]</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+53% pred | 53% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-23% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karan Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C28" s="5" t="n"/>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
+21% pred | 21% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+55% pred | 55% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -2268,60 +2331,25 @@
       <c r="H28" s="5" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-21% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Mrigakshi Jaiswal
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Mrigakshi Jaiswal
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2353,7 +2381,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Supreme HQ, Bandra  |  Class Variety  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -2366,43 +2394,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -2419,8 +2447,8 @@
         <is>
           <t>FIT
 Richard D'Costa
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -2433,14 +2461,21 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -2454,29 +2489,29 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-69% pred | 0% hist
-[]</t>
+69% pred | 69% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -2493,19 +2528,19 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
@@ -2515,16 +2550,16 @@
         <is>
           <t>Barre 57
 Rohan Dahima
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-13% pred | 0% hist
-[]</t>
+Reshma Sharma
+13% pred | 13% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -2538,12 +2573,12 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karanvir Bhatia
-22% pred | 0% hist
-[]</t>
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -2551,8 +2586,8 @@
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -2561,7 +2596,7 @@
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -2570,8 +2605,8 @@
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-86% pred | 0% hist
-[]</t>
+86% pred | 86% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
@@ -2579,25 +2614,32 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
-37% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n"/>
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
-93% pred | 0% hist
-[]</t>
+93% pred | 93% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H9" s="5" t="n"/>
@@ -2609,29 +2651,22 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+100% pred | 100% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -2641,33 +2676,33 @@
         <is>
           <t>FIT
 Vivaran Dhasmana
-92% pred | 0% hist
-[]</t>
+92% pred | 92% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Mrigakshi Jaiswal
-77% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+77% pred | 77% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
+Rohan Dahima
+17% pred | 17% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H11" s="5" t="n"/>
@@ -2682,8 +2717,8 @@
         <is>
           <t>Cardio Barre
 Atulan Purohit
-64% pred | 0% hist
-[]</t>
+64% pred | 64% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -2699,12 +2734,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -2715,21 +2750,21 @@
         <is>
           <t>Barre 57
 Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
+68% pred | 68% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
@@ -2743,16 +2778,16 @@
         <is>
           <t>FIT
 Rohan Dahima
-90% pred | 0% hist
-[]</t>
+90% pred | 90% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
-100% pred | 0% hist
-[]</t>
+100% pred | 100% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
@@ -2763,28 +2798,21 @@
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Reshma Sharma
-21% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -2792,7 +2820,7 @@
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
@@ -2801,54 +2829,54 @@
         <is>
           <t>Barre 57
 Simran Dutt
-64% pred | 0% hist
-[]</t>
+64% pred | 64% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -2858,13 +2886,20 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-56% pred | 0% hist
-[]</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+73% pred | 73% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karanvir Bhatia
+28% pred | 28% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2912,12 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Anisha Shah
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -2904,8 +2939,8 @@
         <is>
           <t>Recovery
 Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H19" s="5" t="n"/>
@@ -2922,12 +2957,12 @@
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Richard D'Costa
-14% pred | 0% hist
-[]</t>
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2977,12 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-19% pred | 0% hist
-[]</t>
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H21" s="5" t="n"/>
@@ -2959,12 +2994,12 @@
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
@@ -2974,7 +3009,7 @@
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
@@ -2983,82 +3018,82 @@
         <is>
           <t>Barre 57
 Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n"/>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E23" s="5" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karan Bhatia
-34% pred | 0% hist
-[]</t>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-36% pred | 0% hist
-[]</t>
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Richard D'Costa
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -3067,8 +3102,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -3089,8 +3124,8 @@
         <is>
           <t>Barre 57
 Karanvir Bhatia
-46% pred | 0% hist
-[]</t>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
@@ -3100,7 +3135,7 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
@@ -3110,59 +3145,66 @@
         <is>
           <t>Barre 57
 Karan Bhatia
-100% pred | 0% hist
-[]</t>
+100% pred | 100% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Rohan Dahima
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Rohan Dahima
-23% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+23% pred | 23% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
     <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
       <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Mrigakshi Jaiswal
+53% pred | 53% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-49% pred | 0% hist
-[]</t>
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -3170,34 +3212,34 @@
       <c r="H28" s="5" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Karan Bhatia
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
-21% pred | 0% hist
-[]</t>
+21% pred | 21% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pranjali Jain
-55% pred | 0% hist
-[]</t>
+55% pred | 55% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F29" s="5" t="n"/>
@@ -3215,8 +3257,8 @@
         <is>
           <t>Recovery
 Mrigakshi Jaiswal
-56% pred | 0% hist
-[]</t>
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -549,7 +549,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Max Score  |  Week of 2026-05-11</t>
+          <t>Supreme HQ, Bandra  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -562,43 +562,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -637,13 +637,20 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+32% pred | 32% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Vivaran Dhasmana
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
+          <t>Barre 57
+Simran Dutt
+29% pred | 29% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -699,8 +706,8 @@
       <c r="F6" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Rohan Dahima
-31% pred | 31% hist
+Karanvir Bhatia
+17% pred | 17% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -714,25 +721,18 @@
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-24% pred | 24% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-13% pred | 13% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -788,10 +788,10 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Reshma Sharma
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+          <t>Cardio Barre
+Anisha Shah
+7% pred | 7% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -799,17 +799,10 @@
           <t>FIT
 Atulan Purohit
 77% pred | 77% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-93% pred | 93% hist
-[PINNED]</t>
-        </is>
-      </c>
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
@@ -819,23 +812,16 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 49% hist
-[CONSIDER]</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+100% pred | 100% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-85% pred | 85% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
@@ -867,8 +853,8 @@
       <c r="F11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Rohan Dahima
-17% pred | 17% hist
+Karan Bhatia
+15% pred | 15% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -920,21 +906,28 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+4% pred | 4% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 68% hist
-[PINNED]</t>
+Atulan Purohit
+27% pred | 27% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -973,14 +966,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="C15" s="5" t="n"/>
       <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
@@ -1036,15 +1022,15 @@
           <t>Barre 57
 Anisha Shah
 36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -1076,12 +1062,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-28% pred | 28% hist
-[INCLUDE]</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -1172,23 +1158,23 @@
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C22" s="5" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -1215,9 +1201,9 @@
       <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Karanvir Bhatia
+Atulan Purohit
 17% pred | 17% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -1229,7 +1215,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
@@ -1241,8 +1234,8 @@
       <c r="B24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
-24% pred | 24% hist
+Anisha Shah
+34% pred | 34% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1250,8 +1243,8 @@
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Cauveri Vikrant
-36% pred | 36% hist
+Mrigakshi Jaiswal
+29% pred | 29% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1271,12 +1264,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Richard D'Costa
-29% pred | 29% hist
-[DROP]</t>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H24" s="5" t="n"/>
@@ -1297,7 +1290,14 @@
       </c>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+45% pred | 45% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C26" s="5" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -1329,13 +1329,20 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
-100% pred | 100% hist
-[PINNED]</t>
+Karanvir Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1354,14 +1361,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
@@ -1380,20 +1380,20 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+22% pred | 22% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+74% pred | 74% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -1409,29 +1409,29 @@
       <c r="B29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Karan Bhatia
-47% pred | 47% hist
+Anisha Shah
+40% pred | 40% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Cauveri Vikrant
-21% pred | 21% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-55% pred | 55% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n"/>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
     </row>
@@ -1486,7 +1486,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Trainer Hours  |  Week of 2026-05-11</t>
+          <t>Supreme HQ, Bandra  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1499,43 +1499,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -1574,13 +1574,20 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+32% pred | 32% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Vivaran Dhasmana
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
+          <t>Barre 57
+Simran Dutt
+29% pred | 29% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -1624,24 +1631,24 @@
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>08:15</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Rohan Dahima
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n"/>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -1697,10 +1704,10 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Reshma Sharma
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+          <t>Cardio Barre
+Anisha Shah
+7% pred | 7% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1708,17 +1715,10 @@
           <t>FIT
 Atulan Purohit
 77% pred | 77% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-93% pred | 93% hist
-[PINNED]</t>
-        </is>
-      </c>
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
@@ -1728,12 +1728,12 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 49% hist
-[CONSIDER]</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Richard D'Costa
+100% pred | 100% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
@@ -1769,8 +1769,8 @@
       <c r="F10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Rohan Dahima
-17% pred | 17% hist
+Karan Bhatia
+15% pred | 15% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1822,13 +1822,20 @@
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+4% pred | 4% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
+Atulan Purohit
+27% pred | 27% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1931,7 +1938,7 @@
           <t>Barre 57
 Anisha Shah
 36% pred | 36% hist
-[PROTECT_EXACT]</t>
+[PINNED]</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1971,12 +1978,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-28% pred | 28% hist
-[INCLUDE]</t>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -2067,23 +2074,23 @@
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -2110,9 +2117,9 @@
       <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Karanvir Bhatia
+Atulan Purohit
 17% pred | 17% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -2143,8 +2150,8 @@
       <c r="B23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
-24% pred | 24% hist
+Anisha Shah
+34% pred | 34% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2152,8 +2159,8 @@
       <c r="D23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Cauveri Vikrant
-36% pred | 36% hist
+Mrigakshi Jaiswal
+29% pred | 29% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2204,19 +2211,19 @@
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
@@ -2228,9 +2235,9 @@
       <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
-100% pred | 100% hist
-[PINNED]</t>
+Karanvir Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -2249,14 +2256,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-58% pred | 58% hist
-[PINNED]</t>
-        </is>
-      </c>
+      <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
     </row>
@@ -2283,12 +2283,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+74% pred | 74% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F27" s="5" t="n"/>
@@ -2304,29 +2304,29 @@
       <c r="B28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Karan Bhatia
-47% pred | 47% hist
+Anisha Shah
+40% pred | 40% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Cauveri Vikrant
-21% pred | 21% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-55% pred | 55% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n"/>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
     </row>
@@ -2381,7 +2381,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supreme HQ, Bandra  |  Class Variety  |  Week of 2026-05-11</t>
+          <t>Supreme HQ, Bandra  |  Class Variety  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -2394,43 +2394,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -2469,13 +2469,20 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+32% pred | 32% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Vivaran Dhasmana
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
+          <t>Barre 57
+Simran Dutt
+29% pred | 29% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -2546,25 +2553,18 @@
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-24% pred | 24% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Reshma Sharma
-13% pred | 13% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
@@ -2620,10 +2620,10 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Reshma Sharma
-37% pred | 37% hist
-[PROTECT_EXACT]</t>
+          <t>Cardio Barre
+Anisha Shah
+7% pred | 7% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2631,17 +2631,10 @@
           <t>FIT
 Atulan Purohit
 77% pred | 77% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-93% pred | 93% hist
-[PINNED]</t>
-        </is>
-      </c>
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
@@ -2692,8 +2685,8 @@
       <c r="F11" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
-Rohan Dahima
-17% pred | 17% hist
+Karan Bhatia
+15% pred | 15% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2745,13 +2738,20 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+4% pred | 4% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
+Atulan Purohit
+27% pred | 27% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -2854,15 +2854,15 @@
           <t>Barre 57
 Anisha Shah
 36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+17% pred | 17% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -2894,12 +2894,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karanvir Bhatia
-28% pred | 28% hist
-[INCLUDE]</t>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
@@ -2990,23 +2990,23 @@
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C22" s="5" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -3033,9 +3033,9 @@
       <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Karanvir Bhatia
+Atulan Purohit
 17% pred | 17% hist
-[CONSIDER]</t>
+[DROP]</t>
         </is>
       </c>
       <c r="E23" s="5" t="n"/>
@@ -3047,7 +3047,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
@@ -3059,8 +3066,8 @@
       <c r="B24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Anmol Sharma
-24% pred | 24% hist
+Anisha Shah
+34% pred | 34% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -3068,8 +3075,8 @@
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Cauveri Vikrant
-36% pred | 36% hist
+Mrigakshi Jaiswal
+29% pred | 29% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -3089,7 +3096,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G24" s="5" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
@@ -3108,7 +3122,14 @@
       </c>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+45% pred | 45% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
@@ -3120,19 +3141,19 @@
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C26" s="5" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -3144,9 +3165,9 @@
       <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
-100% pred | 100% hist
-[PINNED]</t>
+Karanvir Bhatia
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -3165,14 +3186,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
@@ -3191,20 +3205,20 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+22% pred | 22% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+74% pred | 74% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="F28" s="5" t="n"/>
@@ -3220,29 +3234,29 @@
       <c r="B29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
-Karan Bhatia
-47% pred | 47% hist
+Anisha Shah
+40% pred | 40% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
 Cauveri Vikrant
-21% pred | 21% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pranjali Jain
-55% pred | 55% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n"/>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
     </row>

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -47,6 +47,10 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
@@ -54,10 +58,6 @@
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -93,17 +93,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD5D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,10 +160,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -613,8 +613,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
@@ -622,8 +622,8 @@
         <is>
           <t>FIT
 Richard D'Costa
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -636,14 +636,21 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -657,60 +664,60 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-69% pred | 0% hist
-[]</t>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+27% pred | 27% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>08:15</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
@@ -722,12 +729,12 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-15% pred | 0% hist
-[]</t>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -736,7 +743,7 @@
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -745,8 +752,8 @@
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-86% pred | 0% hist
-[]</t>
+86% pred | 86% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -754,8 +761,8 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -763,16 +770,16 @@
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 0% hist
-[]</t>
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
-93% pred | 0% hist
-[]</t>
+93% pred | 93% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
@@ -783,20 +790,13 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Rohan Dahima
-9% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
+88% pred | 88% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
@@ -806,7 +806,7 @@
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -816,33 +816,33 @@
         <is>
           <t>FIT
 Vivaran Dhasmana
-92% pred | 0% hist
-[]</t>
+92% pred | 92% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H10" s="5" t="n"/>
@@ -850,182 +850,203 @@
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+64% pred | 64% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-64% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+Rohan Dahima
+90% pred | 90% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
+100% pred | 100% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+64% pred | 64% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+17% pred | 17% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+33% pred | 33% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+14% pred | 14% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -1033,41 +1054,48 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+73% pred | 73% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+43% pred | 43% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1075,213 +1103,206 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-19% pred | 0% hist
-[]</t>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>18:15</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>19:15</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-74% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karanvir Bhatia
-71% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -1289,25 +1310,95 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+52% pred | 52% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1323,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1403,8 +1494,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
@@ -1412,8 +1503,8 @@
         <is>
           <t>FIT
 Richard D'Costa
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -1426,18 +1517,32 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+26% pred | 26% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
@@ -1447,60 +1552,60 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-69% pred | 0% hist
-[]</t>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+27% pred | 27% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>08:15</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
@@ -1512,12 +1617,12 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-15% pred | 0% hist
-[]</t>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -1526,7 +1631,7 @@
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1535,8 +1640,8 @@
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-86% pred | 0% hist
-[]</t>
+86% pred | 86% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -1544,8 +1649,8 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -1553,16 +1658,16 @@
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 0% hist
-[]</t>
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
-93% pred | 0% hist
-[]</t>
+93% pred | 93% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
@@ -1573,20 +1678,13 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Rohan Dahima
-9% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
+88% pred | 88% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
@@ -1596,7 +1694,7 @@
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -1606,33 +1704,33 @@
         <is>
           <t>FIT
 Vivaran Dhasmana
-92% pred | 0% hist
-[]</t>
+92% pred | 92% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H10" s="5" t="n"/>
@@ -1640,182 +1738,217 @@
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+64% pred | 64% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-64% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+Rohan Dahima
+90% pred | 90% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
+100% pred | 100% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-56% pred | 0% hist
-[]</t>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+64% pred | 64% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+17% pred | 17% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 20% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+33% pred | 33% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+14% pred | 14% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -1823,41 +1956,55 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+73% pred | 73% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+43% pred | 43% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+85% pred | 85% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1865,213 +2012,206 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-19% pred | 0% hist
-[]</t>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>18:15</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>19:15</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-74% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karanvir Bhatia
-71% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -2079,25 +2219,95 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+52% pred | 52% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2113,7 +2323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2193,8 +2403,8 @@
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
@@ -2202,8 +2412,8 @@
         <is>
           <t>FIT
 Richard D'Costa
-42% pred | 0% hist
-[]</t>
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -2216,14 +2426,21 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Vivaran Dhasmana
-34% pred | 0% hist
-[]</t>
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -2237,60 +2454,60 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Bret Saldanha
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-69% pred | 0% hist
-[]</t>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+27% pred | 27% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>08:15</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
     </row>
@@ -2302,12 +2519,12 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-15% pred | 0% hist
-[]</t>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -2316,7 +2533,7 @@
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -2325,8 +2542,8 @@
         <is>
           <t>Cardio Barre
 Cauveri Vikrant
-86% pred | 0% hist
-[]</t>
+86% pred | 86% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -2334,8 +2551,8 @@
         <is>
           <t>Barre 57
 Reshma Sharma
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E8" s="5" t="n"/>
@@ -2343,16 +2560,16 @@
         <is>
           <t>FIT
 Atulan Purohit
-77% pred | 0% hist
-[]</t>
+77% pred | 77% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
-93% pred | 0% hist
-[]</t>
+93% pred | 93% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
@@ -2363,20 +2580,13 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Rohan Dahima
-9% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Mrigakshi Jaiswal
-88% pred | 0% hist
-[]</t>
+88% pred | 88% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D9" s="5" t="n"/>
@@ -2386,7 +2596,7 @@
       <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
@@ -2396,33 +2606,33 @@
         <is>
           <t>FIT
 Vivaran Dhasmana
-92% pred | 0% hist
-[]</t>
+92% pred | 92% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
+68% pred | 68% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Vivaran Dhasmana
-60% pred | 0% hist
-[]</t>
+60% pred | 60% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H10" s="5" t="n"/>
@@ -2430,182 +2640,203 @@
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 0% hist
-[]</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+64% pred | 64% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Reshma Sharma
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simran Dutt
-64% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>FIT
-Vivaran Dhasmana
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+Rohan Dahima
+90% pred | 90% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karanvir Bhatia
-17% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
+100% pred | 100% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Rohan Dahima
-85% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Cauveri Vikrant
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+64% pred | 64% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Karanvir Bhatia
+17% pred | 17% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Anisha Shah
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+33% pred | 33% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+14% pred | 14% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -2613,41 +2844,48 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+73% pred | 73% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+43% pred | 43% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Anisha Shah
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -2655,213 +2893,206 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-19% pred | 0% hist
-[]</t>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Vivaran Dhasmana
+55% pred | 55% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
-53% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
-24% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Raunak Khemuka
-15% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Simonelle De Vitre
-16% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>18:15</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Mrigakshi Jaiswal
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+29% pred | 29% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+24% pred | 24% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Raunak Khemuka
+15% pred | 15% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Mrigakshi Jaiswal
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>19:15</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Simonelle De Vitre
-52% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Mrigakshi Jaiswal
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-74% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Karanvir Bhatia
-71% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -2869,25 +3100,95 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B27" s="5" t="n"/>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Karanvir Bhatia
-42% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Simonelle De Vitre
+52% pred | 52% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+71% pred | 71% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Karanvir Bhatia
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -609,14 +609,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
@@ -639,8 +632,8 @@
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
-49% pred | 49% hist
+Cauveri Vikrant
+50% pred | 50% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -648,9 +641,9 @@
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Vivaran Dhasmana
+Reshma Sharma
 34% pred | 34% hist
-[PROTECT_EXACT]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -684,7 +677,7 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
+Anisha Shah
 27% pred | 27% hist
 [CONSIDER]</t>
         </is>
@@ -701,16 +694,16 @@
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
+Mrigakshi Jaiswal
 24% pred | 24% hist
 [CONSIDER]</t>
         </is>
@@ -722,19 +715,19 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
+15% pred | 15% hist
+[DROP]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -777,42 +770,21 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-93% pred | 93% hist
-[PINNED]</t>
+Atulan Purohit
+69% pred | 69% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-88% pred | 88% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -820,8 +792,8 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -829,7 +801,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
@@ -837,11 +809,32 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 60% hist
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+33% pred | 33% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -850,15 +843,15 @@
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-64% pred | 64% hist
-[PINNED]</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -866,63 +859,42 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 68% hist
-[PINNED]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
           <t>FIT
-Rohan Dahima
-90% pred | 90% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+Atulan Purohit
+82% pred | 82% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -931,15 +903,15 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -947,25 +919,25 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -973,7 +945,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -981,72 +953,93 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+65% pred | 65% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+27% pred | 27% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Anisha Shah
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-17% pred | 17% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+Anmol Sharma
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-33% pred | 33% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-14% pred | 14% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -1054,20 +1047,13 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-73% pred | 73% hist
-[PINNED]</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="n"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-43% pred | 43% hist
-[CONSIDER]</t>
+          <t>Cardio Barre
+Anmol Sharma
+28% pred | 28% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1064,14 @@
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+85% pred | 85% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -1090,7 +1083,14 @@
       </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1106,8 +1106,8 @@
       <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Vivaran Dhasmana
-55% pred | 55% hist
+Pranjali Jain
+41% pred | 41% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1116,28 +1116,35 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -1145,7 +1152,35 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1153,15 +1188,36 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+43% pred | 43% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -1169,7 +1225,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -1177,9 +1233,9 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1187,16 +1243,16 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1204,7 +1260,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -1212,8 +1268,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1221,24 +1277,31 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-24% pred | 24% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1246,22 +1309,29 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pranjali Jain
+29% pred | 29% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -1269,19 +1339,26 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1289,15 +1366,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+34% pred | 34% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
@@ -1305,18 +1382,18 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -1324,7 +1401,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1332,7 +1409,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1340,17 +1417,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1358,9 +1435,9 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -1368,7 +1445,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Cauveri Vikrant
@@ -1376,17 +1453,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -1394,11 +1471,11 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1490,14 +1567,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
@@ -1520,29 +1590,15 @@
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
-49% pred | 49% hist
+Cauveri Vikrant
+50% pred | 50% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Vivaran Dhasmana
-34% pred | 34% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
@@ -1572,7 +1628,7 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
+Anisha Shah
 27% pred | 27% hist
 [CONSIDER]</t>
         </is>
@@ -1589,16 +1645,16 @@
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
+Reshma Sharma
 24% pred | 24% hist
 [CONSIDER]</t>
         </is>
@@ -1610,19 +1666,19 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
+15% pred | 15% hist
+[DROP]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -1665,42 +1721,21 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-93% pred | 93% hist
-[PINNED]</t>
+Atulan Purohit
+69% pred | 69% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-88% pred | 88% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -1708,8 +1743,8 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -1717,7 +1752,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
@@ -1725,11 +1760,39 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 60% hist
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+33% pred | 33% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1738,86 +1801,58 @@
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-64% pred | 64% hist
-[PINNED]</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 68% hist
-[PINNED]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
           <t>FIT
-Rohan Dahima
-90% pred | 90% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+Atulan Purohit
+82% pred | 82% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1826,15 +1861,15 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1842,25 +1877,25 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -1868,128 +1903,100 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Vivaran Dhasmana
-42% pred | 42% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+21% pred | 21% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+65% pred | 65% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Anisha Shah
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 17% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 20% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+Anmol Sharma
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-33% pred | 33% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-14% pred | 14% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-73% pred | 73% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-43% pred | 43% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-85% pred | 85% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Anisha Shah
@@ -1997,14 +2004,35 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+41% pred | 41% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -2012,20 +2040,27 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Vivaran Dhasmana
-55% pred | 55% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -2033,20 +2068,20 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -2054,15 +2089,15 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-19% pred | 19% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -2081,7 +2116,7 @@
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Reshma Sharma
+Mrigakshi Jaiswal
 29% pred | 29% hist
 [CONSIDER]</t>
         </is>
@@ -2130,13 +2165,20 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-24% pred | 24% hist
-[CONSIDER]</t>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H23" s="5" t="n"/>
@@ -2156,7 +2198,14 @@
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pranjali Jain
+29% pred | 29% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
@@ -2181,7 +2230,14 @@
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Richard D'Costa
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
@@ -2198,12 +2254,12 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+34% pred | 34% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -2323,7 +2379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2399,14 +2455,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
@@ -2429,8 +2478,8 @@
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Reshma Sharma
-49% pred | 49% hist
+Cauveri Vikrant
+50% pred | 50% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2438,9 +2487,9 @@
       <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Vivaran Dhasmana
+Reshma Sharma
 34% pred | 34% hist
-[PROTECT_EXACT]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="E4" s="5" t="n"/>
@@ -2474,7 +2523,7 @@
       <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
+Anisha Shah
 27% pred | 27% hist
 [CONSIDER]</t>
         </is>
@@ -2491,16 +2540,16 @@
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>08:30</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
+Mrigakshi Jaiswal
 24% pred | 24% hist
 [CONSIDER]</t>
         </is>
@@ -2512,19 +2561,19 @@
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>08:45</t>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
 Vivaran Dhasmana
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
+15% pred | 15% hist
+[DROP]</t>
         </is>
       </c>
       <c r="E7" s="5" t="n"/>
@@ -2567,42 +2616,21 @@
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-93% pred | 93% hist
-[PINNED]</t>
+Atulan Purohit
+69% pred | 69% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-88% pred | 88% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>FIT
 Vivaran Dhasmana
@@ -2610,8 +2638,8 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Anisha Shah
@@ -2619,7 +2647,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Karan Bhatia
@@ -2627,11 +2655,32 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-60% pred | 60% hist
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+33% pred | 33% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2640,15 +2689,15 @@
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Atulan Purohit
-64% pred | 64% hist
-[PINNED]</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -2656,63 +2705,42 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+68% pred | 68% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Atulan Purohit
+34% pred | 34% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Karanvir Bhatia
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-68% pred | 68% hist
-[PINNED]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
           <t>FIT
-Rohan Dahima
-90% pred | 90% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+Atulan Purohit
+82% pred | 82% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2721,15 +2749,15 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -2737,25 +2765,25 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Rohan Dahima
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anisha Shah
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Simran Dutt
@@ -2763,7 +2791,7 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Vivaran Dhasmana
@@ -2771,72 +2799,93 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Vivaran Dhasmana
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simonelle De Vitre
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Bret Saldanha
+65% pred | 65% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+27% pred | 27% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Anisha Shah
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Karanvir Bhatia
-17% pred | 17% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-75% pred | 75% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+Anmol Sharma
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-33% pred | 33% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-14% pred | 14% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Cauveri Vikrant
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -2844,20 +2893,13 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-73% pred | 73% hist
-[PINNED]</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="n"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Rohan Dahima
-43% pred | 43% hist
-[CONSIDER]</t>
+          <t>Cardio Barre
+Anmol Sharma
+28% pred | 28% hist
+[INCLUDE]</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2910,14 @@
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Vivaran Dhasmana
+85% pred | 85% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -2880,7 +2929,14 @@
       </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2896,8 +2952,8 @@
       <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Vivaran Dhasmana
-55% pred | 55% hist
+Pranjali Jain
+41% pred | 41% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2906,28 +2962,35 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karanvir Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -2935,7 +2998,35 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2943,15 +3034,36 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+43% pred | 43% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Vivaran Dhasmana
@@ -2959,7 +3071,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Reshma Sharma
@@ -2967,9 +3079,9 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2977,16 +3089,16 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2994,7 +3106,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -3002,8 +3114,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -3011,24 +3123,31 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pranjali Jain
-24% pred | 24% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -3036,22 +3155,29 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pranjali Jain
+29% pred | 29% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Mrigakshi Jaiswal
@@ -3059,19 +3185,26 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -3079,15 +3212,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+34% pred | 34% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
@@ -3095,18 +3228,18 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -3114,7 +3247,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -3122,7 +3255,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -3130,17 +3263,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -3148,9 +3281,9 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -3158,7 +3291,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Cauveri Vikrant
@@ -3166,17 +3299,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -3184,11 +3317,11 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_supreme.xlsx
+++ b/outputs/schedule_supreme.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -886,14 +886,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-82% pred | 82% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G12" s="5" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -919,14 +912,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-27% pred | 27% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
@@ -955,13 +941,20 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simonelle De Vitre
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n"/>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Mat 57
@@ -987,25 +980,18 @@
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-27% pred | 27% hist
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+70% pred | 70% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-35% pred | 35% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -1018,13 +1004,20 @@
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
+Simonelle De Vitre
 54% pred | 54% hist
-[PROTECT_EXACT]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1051,7 +1044,7 @@
       <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Anmol Sharma
+Bret Saldanha
 28% pred | 28% hist
 [INCLUDE]</t>
         </is>
@@ -1064,14 +1057,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-85% pred | 85% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -1083,14 +1069,7 @@
       </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1116,35 +1095,35 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -1152,27 +1131,20 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
@@ -1180,29 +1152,8 @@
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-19% pred | 19% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Richard D'Costa
@@ -1211,48 +1162,48 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-29% pred | 29% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1260,7 +1211,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -1268,8 +1219,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -1277,15 +1235,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-27% pred | 27% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
@@ -1293,15 +1244,15 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -1309,40 +1260,40 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Pranjali Jain
+Richard D'Costa
 29% pred | 29% hist
 [INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -1351,14 +1302,14 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -1366,15 +1317,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
-34% pred | 34% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
@@ -1382,18 +1326,18 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -1401,15 +1345,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -1417,17 +1361,24 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -1435,9 +1386,9 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -1445,7 +1396,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Cauveri Vikrant
@@ -1453,17 +1404,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -1471,11 +1422,11 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1491,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1596,7 +1547,14 @@
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+34% pred | 34% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
@@ -1654,7 +1612,7 @@
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Reshma Sharma
+Mrigakshi Jaiswal
 24% pred | 24% hist
 [CONSIDER]</t>
         </is>
@@ -1777,14 +1735,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
-27% pred | 27% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
@@ -1844,14 +1795,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-82% pred | 82% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G12" s="5" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1877,14 +1821,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-27% pred | 27% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
@@ -1905,21 +1842,28 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Reshma Sharma
-21% pred | 21% hist
-[CONSIDER]</t>
+          <t>Back Body Blaze
+Vivaran Dhasmana
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simonelle De Vitre
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n"/>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Mat 57
@@ -1947,16 +1891,16 @@
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-35% pred | 35% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+70% pred | 70% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -1969,13 +1913,20 @@
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
+Simonelle De Vitre
 54% pred | 54% hist
-[PROTECT_EXACT]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1990,13 +1941,34 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Anisha Shah
@@ -2004,35 +1976,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pranjali Jain
-41% pred | 41% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -2040,27 +1991,20 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Pranjali Jain
+41% pred | 41% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
@@ -2068,20 +2012,27 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-19% pred | 19% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -2089,41 +2040,62 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Richard D'Costa
+43% pred | 43% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Reshma Sharma
 36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Mrigakshi Jaiswal
-29% pred | 29% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2131,16 +2103,16 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2148,7 +2120,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -2156,8 +2128,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -2165,15 +2144,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-27% pred | 27% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
@@ -2181,15 +2153,15 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -2197,56 +2169,56 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Pranjali Jain
+Richard D'Costa
 29% pred | 29% hist
 [INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Richard D'Costa
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Reshma Sharma
+37% pred | 37% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -2254,15 +2226,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
-34% pred | 34% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
@@ -2270,18 +2235,18 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -2289,15 +2254,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -2305,17 +2270,24 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -2323,9 +2295,9 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -2333,7 +2305,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Cauveri Vikrant
@@ -2341,17 +2313,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -2359,11 +2331,11 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2379,7 +2351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2732,14 +2704,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-82% pred | 82% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G12" s="5" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -2765,14 +2730,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anisha Shah
-27% pred | 27% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
@@ -2801,13 +2759,20 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simonelle De Vitre
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n"/>
+          <t>FIT
+Vivaran Dhasmana
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anisha Shah
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Mat 57
@@ -2833,25 +2798,18 @@
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-27% pred | 27% hist
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pranjali Jain
+70% pred | 70% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-35% pred | 35% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -2864,13 +2822,20 @@
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
+Simonelle De Vitre
 54% pred | 54% hist
-[PROTECT_EXACT]</t>
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -2897,7 +2862,7 @@
       <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Anmol Sharma
+Bret Saldanha
 28% pred | 28% hist
 [INCLUDE]</t>
         </is>
@@ -2910,14 +2875,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Vivaran Dhasmana
-85% pred | 85% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -2929,14 +2887,7 @@
       </c>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2962,35 +2913,35 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle Express
+Richard D'Costa
+14% pred | 14% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
@@ -2998,27 +2949,20 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle Express
-Richard D'Costa
-14% pred | 14% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Anmol Sharma
+19% pred | 19% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B22" s="5" t="n"/>
@@ -3026,29 +2970,8 @@
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Anmol Sharma
-19% pred | 19% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Richard D'Costa
@@ -3057,48 +2980,48 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Cauveri Vikrant
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-29% pred | 29% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Cauveri Vikrant
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -3106,7 +3029,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Raunak Khemuka
@@ -3114,8 +3037,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Pranjali Jain
+24% pred | 24% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
@@ -3123,15 +3053,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anisha Shah
-27% pred | 27% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
@@ -3139,15 +3062,15 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Mrigakshi Jaiswal
@@ -3155,40 +3078,40 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Pranjali Jain
+Richard D'Costa
 29% pred | 29% hist
 [INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>PowerCycle
+Mrigakshi Jaiswal
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>PowerCycle
-Mrigakshi Jaiswal
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Reshma Sharma
@@ -3197,14 +3120,14 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Karanvir Bhatia
@@ -3212,15 +3135,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Richard D'Costa
-34% pred | 34% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Mat 57 Express
 Karanvir Bhatia
@@ -3228,18 +3144,18 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Simonelle De Vitre
@@ -3247,15 +3163,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-45% pred | 45% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Cauveri Vikrant
@@ -3263,17 +3179,24 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle
 Anmol Sharma
@@ -3281,9 +3204,9 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>FIT
 Karanvir Bhatia
@@ -3291,7 +3214,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>PowerCycle Express
 Cauveri Vikrant
@@ -3299,17 +3222,17 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Recovery
 Karanvir Bhatia
@@ -3317,11 +3240,11 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
